--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4621" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC37FBC9-C294-47BA-B669-B840C7A7D0EA}"/>
+  <xr:revisionPtr revIDLastSave="4626" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59DD4D9C-384B-4AC4-9D74-85AC71B7BA87}"/>
   <bookViews>
-    <workbookView xWindow="13170" yWindow="1320" windowWidth="25230" windowHeight="16530" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="70" yWindow="190" windowWidth="27140" windowHeight="17750" tabRatio="905" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -4170,14 +4170,14 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -17439,16 +17439,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="162"/>
-      <c r="C45" s="162"/>
-      <c r="D45" s="162"/>
-      <c r="E45" s="162"/>
-      <c r="F45" s="162"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="162"/>
-      <c r="I45" s="162"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="162"/>
+      <c r="B45" s="164"/>
+      <c r="C45" s="164"/>
+      <c r="D45" s="164"/>
+      <c r="E45" s="164"/>
+      <c r="F45" s="164"/>
+      <c r="G45" s="164"/>
+      <c r="H45" s="164"/>
+      <c r="I45" s="164"/>
+      <c r="J45" s="164"/>
+      <c r="K45" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17476,14 +17476,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="164" t="s">
         <v>516</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="O75" s="73">
         <f>Chaindrive!O23</f>
-        <v>3.6842105263157898</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P75" s="1">
         <v>25</v>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="D77" s="23">
         <f>Chaindrive!J26</f>
-        <v>475</v>
+        <v>443.33333333333331</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>347</v>
@@ -28372,11 +28372,11 @@
       </c>
       <c r="C78" s="2">
         <f>D84+0.01</f>
-        <v>475.01</v>
+        <v>443.34333333333331</v>
       </c>
       <c r="D78" s="23">
         <f>Chaindrive!J28</f>
-        <v>712.5</v>
+        <v>665</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>347</v>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="C79" s="2">
         <f>D78+0.01</f>
-        <v>712.51</v>
+        <v>665.01</v>
       </c>
       <c r="D79" s="23">
         <f>Chaindrive!J39</f>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="D84" s="23">
         <f>Chaindrive!J27</f>
-        <v>475</v>
+        <v>443.33333333333331</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>347</v>
@@ -28772,11 +28772,11 @@
       </c>
       <c r="C85" s="2">
         <f>D84+0.01</f>
-        <v>475.01</v>
+        <v>443.34333333333331</v>
       </c>
       <c r="D85" s="23">
         <f>Chaindrive!J29</f>
-        <v>712.5</v>
+        <v>665</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>347</v>
@@ -28833,7 +28833,7 @@
       </c>
       <c r="C86" s="2">
         <f>D85+0.01</f>
-        <v>712.51</v>
+        <v>665.01</v>
       </c>
       <c r="D86" s="23">
         <f>Chaindrive!J39</f>
@@ -31212,7 +31212,7 @@
       <c r="S129" s="1"/>
     </row>
     <row r="130" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="163" t="s">
+      <c r="A130" s="162" t="s">
         <v>498</v>
       </c>
       <c r="B130" s="119" t="s">
@@ -31264,10 +31264,10 @@
         <v>4500</v>
       </c>
       <c r="S130" s="51"/>
-      <c r="U130" s="164"/>
+      <c r="U130" s="163"/>
     </row>
     <row r="131" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="163" t="s">
+      <c r="A131" s="162" t="s">
         <v>499</v>
       </c>
       <c r="B131" s="119" t="s">
@@ -31319,7 +31319,7 @@
         <v>4500</v>
       </c>
       <c r="S131" s="51"/>
-      <c r="U131" s="164"/>
+      <c r="U131" s="163"/>
     </row>
     <row r="132" spans="1:21" s="102" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="99" t="s">
@@ -31627,209 +31627,225 @@
         <v>1257.99</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="3" t="s">
+    <row r="138" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="162" t="s">
         <v>364</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="C138" s="1">
+      <c r="C138" s="51">
         <f t="shared" si="10"/>
         <v>550.01</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="46">
         <v>550</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E138" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="46">
         <v>24</v>
       </c>
-      <c r="G138" s="1">
+      <c r="G138" s="51">
         <v>415</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="H138" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I138" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="J138" s="51"/>
+      <c r="K138" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="L138" s="1">
-        <v>55</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N138" s="1" t="s">
+      <c r="L138" s="51">
+        <v>55</v>
+      </c>
+      <c r="M138" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="N138" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O138" s="6">
+      <c r="O138" s="46">
         <v>20</v>
       </c>
-      <c r="P138" s="1">
+      <c r="P138" s="51">
         <v>11</v>
       </c>
-      <c r="R138" s="6">
+      <c r="Q138" s="51"/>
+      <c r="R138" s="46">
         <v>1500</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="3" t="s">
+      <c r="S138" s="46"/>
+      <c r="U138" s="163"/>
+    </row>
+    <row r="139" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="162" t="s">
         <v>365</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="C139" s="1">
+      <c r="C139" s="51">
         <f t="shared" si="10"/>
         <v>550.01</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="46">
         <v>750</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F139" s="46">
         <v>24</v>
       </c>
-      <c r="G139" s="1">
+      <c r="G139" s="51">
         <v>415</v>
       </c>
-      <c r="H139" s="1" t="s">
+      <c r="H139" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="I139" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="J139" s="51"/>
+      <c r="K139" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="L139" s="1">
-        <v>55</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N139" s="1" t="s">
+      <c r="L139" s="51">
+        <v>55</v>
+      </c>
+      <c r="M139" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="N139" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O139" s="6">
+      <c r="O139" s="46">
         <v>20</v>
       </c>
-      <c r="P139" s="1">
+      <c r="P139" s="51">
         <v>12</v>
       </c>
-      <c r="R139" s="6">
+      <c r="Q139" s="51"/>
+      <c r="R139" s="46">
         <v>2000</v>
       </c>
-    </row>
-    <row r="140" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="3" t="s">
+      <c r="S139" s="46"/>
+      <c r="U139" s="163"/>
+    </row>
+    <row r="140" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="162" t="s">
         <v>366</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="C140" s="1">
+      <c r="C140" s="51">
         <f t="shared" si="10"/>
         <v>750.01</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="46">
         <v>1000</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="46">
         <v>24</v>
       </c>
-      <c r="G140" s="1">
+      <c r="G140" s="51">
         <v>415</v>
       </c>
-      <c r="H140" s="1" t="s">
+      <c r="H140" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I140" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="K140" s="1" t="s">
+      <c r="J140" s="51"/>
+      <c r="K140" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="L140" s="1">
-        <v>55</v>
-      </c>
-      <c r="M140" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N140" s="1" t="s">
+      <c r="L140" s="51">
+        <v>55</v>
+      </c>
+      <c r="M140" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="N140" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O140" s="6">
+      <c r="O140" s="46">
         <v>20</v>
       </c>
-      <c r="P140" s="1">
+      <c r="P140" s="51">
         <v>11</v>
       </c>
-      <c r="R140" s="6">
+      <c r="Q140" s="51"/>
+      <c r="R140" s="46">
         <v>3000</v>
       </c>
-    </row>
-    <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="3" t="s">
+      <c r="S140" s="46"/>
+      <c r="U140" s="163"/>
+    </row>
+    <row r="141" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="162" t="s">
         <v>494</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C141" s="51">
         <f t="shared" si="10"/>
         <v>1000.01</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="46">
         <v>1200</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="46">
         <v>12</v>
       </c>
-      <c r="G141" s="1">
+      <c r="G141" s="51">
         <v>415</v>
       </c>
-      <c r="H141" s="1" t="s">
+      <c r="H141" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="I141" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="K141" s="1" t="s">
+      <c r="J141" s="51"/>
+      <c r="K141" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="L141" s="1">
-        <v>55</v>
-      </c>
-      <c r="M141" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N141" s="1" t="s">
+      <c r="L141" s="51">
+        <v>55</v>
+      </c>
+      <c r="M141" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="N141" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O141" s="6">
+      <c r="O141" s="46">
         <v>20</v>
       </c>
-      <c r="P141" s="1">
+      <c r="P141" s="51">
         <v>10</v>
       </c>
-      <c r="R141" s="6">
+      <c r="Q141" s="51"/>
+      <c r="R141" s="46">
         <v>3000</v>
       </c>
+      <c r="S141" s="46"/>
+      <c r="U141" s="163"/>
     </row>
     <row r="142" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
@@ -32944,11 +32960,11 @@
         <v>230</v>
       </c>
       <c r="N23" s="70">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="O23" s="70">
         <f t="shared" ref="O23" si="25">N23/G23</f>
-        <v>3.6842105263157898</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P23" s="6">
         <v>61.09</v>
@@ -33063,7 +33079,7 @@
         <v>80</v>
       </c>
       <c r="L25" s="74">
-        <f t="shared" ref="L25" si="32">K25/G25</f>
+        <f>K25/G25</f>
         <v>21.05263157894737</v>
       </c>
       <c r="M25" s="70">
@@ -33073,7 +33089,7 @@
         <v>20</v>
       </c>
       <c r="O25" s="70">
-        <f t="shared" ref="O25" si="33">N25/G25</f>
+        <f t="shared" ref="O25" si="32">N25/G25</f>
         <v>5.2631578947368425</v>
       </c>
       <c r="P25" s="6">
@@ -33109,24 +33125,24 @@
         <v>30</v>
       </c>
       <c r="G26" s="74">
-        <f t="shared" ref="G26:G28" si="34">E26/C26</f>
+        <f t="shared" ref="G26:G28" si="33">E26/C26</f>
         <v>3.1666666666666665</v>
       </c>
       <c r="H26" s="70" t="s">
         <v>388</v>
       </c>
       <c r="I26" s="70">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J26" s="72">
         <f>I26*G26</f>
-        <v>475</v>
+        <v>443.33333333333331</v>
       </c>
       <c r="K26" s="70">
         <v>80</v>
       </c>
       <c r="L26" s="74">
-        <f t="shared" ref="L26" si="35">K26/G26</f>
+        <f t="shared" ref="L26" si="34">K26/G26</f>
         <v>25.263157894736842</v>
       </c>
       <c r="M26" s="70">
@@ -33136,7 +33152,7 @@
         <v>20</v>
       </c>
       <c r="O26" s="70">
-        <f t="shared" ref="O26:O28" si="36">N26/G26</f>
+        <f t="shared" ref="O26:O28" si="35">N26/G26</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="P26" s="6">
@@ -33179,17 +33195,17 @@
         <v>388</v>
       </c>
       <c r="I27" s="70">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J27" s="72">
         <f>I27*G27</f>
-        <v>475</v>
+        <v>443.33333333333331</v>
       </c>
       <c r="K27" s="70">
         <v>80</v>
       </c>
       <c r="L27" s="74">
-        <f t="shared" ref="L27" si="37">K27/G27</f>
+        <f t="shared" ref="L27" si="36">K27/G27</f>
         <v>25.263157894736842</v>
       </c>
       <c r="M27" s="70">
@@ -33235,18 +33251,18 @@
         <v>40</v>
       </c>
       <c r="G28" s="74">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>4.75</v>
       </c>
       <c r="H28" s="70" t="s">
         <v>388</v>
       </c>
       <c r="I28" s="70">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J28" s="72">
         <f>I28*G28</f>
-        <v>712.5</v>
+        <v>665</v>
       </c>
       <c r="K28" s="70">
         <v>80</v>
@@ -33262,7 +33278,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="70">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>4.2105263157894735</v>
       </c>
       <c r="P28" s="6">
@@ -33298,18 +33314,18 @@
         <v>40</v>
       </c>
       <c r="G29" s="74">
-        <f t="shared" ref="G29" si="38">E29/C29</f>
+        <f t="shared" ref="G29" si="37">E29/C29</f>
         <v>4.75</v>
       </c>
       <c r="H29" s="70" t="s">
         <v>388</v>
       </c>
       <c r="I29" s="70">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J29" s="72">
         <f>I29*G29</f>
-        <v>712.5</v>
+        <v>665</v>
       </c>
       <c r="K29" s="70">
         <v>80</v>
@@ -33325,7 +33341,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="70">
-        <f t="shared" ref="O29" si="39">N29/G29</f>
+        <f t="shared" ref="O29" si="38">N29/G29</f>
         <v>4.2105263157894735</v>
       </c>
       <c r="P29" s="6">
@@ -33378,7 +33394,7 @@
         <v>40</v>
       </c>
       <c r="G32" s="73">
-        <f t="shared" ref="G32" si="40">E32/C32</f>
+        <f t="shared" ref="G32" si="39">E32/C32</f>
         <v>3.8</v>
       </c>
       <c r="H32" s="6" t="s">
@@ -33388,14 +33404,14 @@
         <v>400</v>
       </c>
       <c r="J32" s="71">
-        <f t="shared" ref="J32" si="41">I32*G32</f>
+        <f t="shared" ref="J32" si="40">I32*G32</f>
         <v>1520</v>
       </c>
       <c r="K32" s="1">
         <v>24</v>
       </c>
       <c r="L32" s="73">
-        <f t="shared" ref="L32" si="42">K32/G32</f>
+        <f t="shared" ref="L32" si="41">K32/G32</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M32" s="6">
@@ -33405,7 +33421,7 @@
         <v>40</v>
       </c>
       <c r="O32" s="70">
-        <f t="shared" ref="O32" si="43">N32/G32</f>
+        <f t="shared" ref="O32" si="42">N32/G32</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P32" s="6">
@@ -33415,7 +33431,7 @@
         <v>461</v>
       </c>
       <c r="R32" s="6">
-        <f t="shared" ref="R32" si="44">D32</f>
+        <f t="shared" ref="R32" si="43">D32</f>
         <v>40</v>
       </c>
       <c r="S32" s="6">
@@ -33442,7 +33458,7 @@
         <v>40</v>
       </c>
       <c r="G33" s="73">
-        <f t="shared" ref="G33" si="45">E33/C33</f>
+        <f t="shared" ref="G33" si="44">E33/C33</f>
         <v>3.8</v>
       </c>
       <c r="H33" s="6" t="s">
@@ -33452,14 +33468,14 @@
         <v>400</v>
       </c>
       <c r="J33" s="71">
-        <f t="shared" ref="J33" si="46">I33*G33</f>
+        <f t="shared" ref="J33" si="45">I33*G33</f>
         <v>1520</v>
       </c>
       <c r="K33" s="1">
         <v>24</v>
       </c>
       <c r="L33" s="73">
-        <f t="shared" ref="L33" si="47">K33/G33</f>
+        <f t="shared" ref="L33" si="46">K33/G33</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M33" s="6">
@@ -33469,7 +33485,7 @@
         <v>40</v>
       </c>
       <c r="O33" s="70">
-        <f t="shared" ref="O33:O35" si="48">N33/G33</f>
+        <f t="shared" ref="O33:O35" si="47">N33/G33</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P33" s="6">
@@ -33479,7 +33495,7 @@
         <v>461</v>
       </c>
       <c r="R33" s="6">
-        <f t="shared" ref="R33:R35" si="49">D33</f>
+        <f t="shared" ref="R33:R35" si="48">D33</f>
         <v>40</v>
       </c>
       <c r="S33" s="6">
@@ -33506,7 +33522,7 @@
         <v>55</v>
       </c>
       <c r="G34" s="73">
-        <f t="shared" ref="G34:G35" si="50">E34/C34</f>
+        <f t="shared" ref="G34:G35" si="49">E34/C34</f>
         <v>3.8</v>
       </c>
       <c r="H34" s="6" t="s">
@@ -33516,14 +33532,14 @@
         <v>600</v>
       </c>
       <c r="J34" s="71">
-        <f t="shared" ref="J34:J35" si="51">I34*G34</f>
+        <f t="shared" ref="J34:J35" si="50">I34*G34</f>
         <v>2280</v>
       </c>
       <c r="K34" s="1">
         <v>24</v>
       </c>
       <c r="L34" s="73">
-        <f t="shared" ref="L34:L35" si="52">K34/G34</f>
+        <f t="shared" ref="L34:L35" si="51">K34/G34</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M34" s="6">
@@ -33533,7 +33549,7 @@
         <v>60</v>
       </c>
       <c r="O34" s="70">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P34" s="6">
@@ -33543,7 +33559,7 @@
         <v>461</v>
       </c>
       <c r="R34" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>55</v>
       </c>
       <c r="S34" s="6">
@@ -33570,7 +33586,7 @@
         <v>55</v>
       </c>
       <c r="G35" s="73">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>3.8</v>
       </c>
       <c r="H35" s="6" t="s">
@@ -33580,14 +33596,14 @@
         <v>800</v>
       </c>
       <c r="J35" s="71">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>3040</v>
       </c>
       <c r="K35" s="1">
         <v>24</v>
       </c>
       <c r="L35" s="73">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>6.3157894736842106</v>
       </c>
       <c r="M35" s="6">
@@ -33597,7 +33613,7 @@
         <v>60</v>
       </c>
       <c r="O35" s="70">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P35" s="6">
@@ -33607,7 +33623,7 @@
         <v>576</v>
       </c>
       <c r="R35" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>55</v>
       </c>
       <c r="S35" s="6">
@@ -33634,7 +33650,7 @@
         <v>55</v>
       </c>
       <c r="G36" s="73">
-        <f t="shared" ref="G36" si="53">E36/C36</f>
+        <f t="shared" ref="G36" si="52">E36/C36</f>
         <v>3.8</v>
       </c>
       <c r="H36" s="6" t="s">
@@ -33644,14 +33660,14 @@
         <v>800</v>
       </c>
       <c r="J36" s="71">
-        <f t="shared" ref="J36" si="54">I36*G36</f>
+        <f t="shared" ref="J36" si="53">I36*G36</f>
         <v>3040</v>
       </c>
       <c r="K36" s="1">
         <v>24</v>
       </c>
       <c r="L36" s="73">
-        <f t="shared" ref="L36" si="55">K36/G36</f>
+        <f t="shared" ref="L36" si="54">K36/G36</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M36" s="6">
@@ -33661,7 +33677,7 @@
         <v>60</v>
       </c>
       <c r="O36" s="70">
-        <f t="shared" ref="O36" si="56">N36/G36</f>
+        <f t="shared" ref="O36" si="55">N36/G36</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P36" s="6">
@@ -33671,7 +33687,7 @@
         <v>576</v>
       </c>
       <c r="R36" s="6">
-        <f t="shared" ref="R36" si="57">D36</f>
+        <f t="shared" ref="R36" si="56">D36</f>
         <v>55</v>
       </c>
       <c r="S36" s="6">
@@ -33698,7 +33714,7 @@
         <v>40</v>
       </c>
       <c r="G39" s="73">
-        <f t="shared" ref="G39" si="58">E39/C39</f>
+        <f t="shared" ref="G39" si="57">E39/C39</f>
         <v>3.8</v>
       </c>
       <c r="H39" s="6" t="s">
@@ -33708,14 +33724,14 @@
         <v>300</v>
       </c>
       <c r="J39" s="71">
-        <f t="shared" ref="J39" si="59">I39*G39</f>
+        <f t="shared" ref="J39" si="58">I39*G39</f>
         <v>1140</v>
       </c>
       <c r="K39" s="1">
         <v>40</v>
       </c>
       <c r="L39" s="73">
-        <f t="shared" ref="L39" si="60">K39/G39</f>
+        <f t="shared" ref="L39" si="59">K39/G39</f>
         <v>10.526315789473685</v>
       </c>
       <c r="M39" s="6" t="s">
@@ -33761,7 +33777,7 @@
         <v>40</v>
       </c>
       <c r="G40" s="73">
-        <f t="shared" ref="G40" si="61">E40/C40</f>
+        <f t="shared" ref="G40" si="60">E40/C40</f>
         <v>3.8</v>
       </c>
       <c r="H40" s="6" t="s">
@@ -33771,14 +33787,14 @@
         <v>300</v>
       </c>
       <c r="J40" s="71">
-        <f t="shared" ref="J40" si="62">I40*G40</f>
+        <f t="shared" ref="J40" si="61">I40*G40</f>
         <v>1140</v>
       </c>
       <c r="K40" s="1">
         <v>40</v>
       </c>
       <c r="L40" s="73">
-        <f t="shared" ref="L40" si="63">K40/G40</f>
+        <f t="shared" ref="L40" si="62">K40/G40</f>
         <v>10.526315789473685</v>
       </c>
       <c r="M40" s="6" t="s">
@@ -33824,7 +33840,7 @@
         <v>55</v>
       </c>
       <c r="G41" s="73">
-        <f t="shared" ref="G41" si="64">E41/C41</f>
+        <f t="shared" ref="G41" si="63">E41/C41</f>
         <v>3.8</v>
       </c>
       <c r="H41" s="6" t="s">
@@ -33834,7 +33850,7 @@
         <v>500</v>
       </c>
       <c r="J41" s="71">
-        <f t="shared" ref="J41" si="65">I41*G41</f>
+        <f t="shared" ref="J41" si="64">I41*G41</f>
         <v>1900</v>
       </c>
       <c r="K41" s="1">
@@ -33887,7 +33903,7 @@
         <v>55</v>
       </c>
       <c r="G42" s="73">
-        <f t="shared" ref="G42" si="66">E42/C42</f>
+        <f t="shared" ref="G42" si="65">E42/C42</f>
         <v>3.8</v>
       </c>
       <c r="H42" s="6" t="s">
@@ -33897,7 +33913,7 @@
         <v>800</v>
       </c>
       <c r="J42" s="71">
-        <f t="shared" ref="J42" si="67">I42*G42</f>
+        <f t="shared" ref="J42" si="66">I42*G42</f>
         <v>3040</v>
       </c>
       <c r="K42" s="1">
@@ -33950,7 +33966,7 @@
         <v>55</v>
       </c>
       <c r="G43" s="73">
-        <f t="shared" ref="G43" si="68">E43/C43</f>
+        <f t="shared" ref="G43" si="67">E43/C43</f>
         <v>3.8</v>
       </c>
       <c r="H43" s="6" t="s">
@@ -33960,7 +33976,7 @@
         <v>800</v>
       </c>
       <c r="J43" s="71">
-        <f t="shared" ref="J43" si="69">I43*G43</f>
+        <f t="shared" ref="J43" si="68">I43*G43</f>
         <v>3040</v>
       </c>
       <c r="K43" s="1">
@@ -34027,7 +34043,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="73">
-        <f t="shared" ref="L45:L50" si="70">K45/G45</f>
+        <f t="shared" ref="L45:L50" si="69">K45/G45</f>
         <v>6.1311475409836058</v>
       </c>
       <c r="M45" s="6">
@@ -34054,7 +34070,7 @@
         <v>50</v>
       </c>
       <c r="G46" s="73">
-        <f t="shared" ref="G46:G47" si="71">E46/C46</f>
+        <f t="shared" ref="G46:G47" si="70">E46/C46</f>
         <v>5.5555555555555554</v>
       </c>
       <c r="H46" s="6" t="s">
@@ -34064,14 +34080,14 @@
         <v>62</v>
       </c>
       <c r="J46" s="23">
-        <f t="shared" ref="J46:J49" si="72">I46*G46</f>
+        <f t="shared" ref="J46:J49" si="71">I46*G46</f>
         <v>344.44444444444446</v>
       </c>
       <c r="K46" s="1">
         <v>34</v>
       </c>
       <c r="L46" s="73">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>6.12</v>
       </c>
       <c r="M46" s="6">
@@ -34095,7 +34111,7 @@
         <v>64</v>
       </c>
       <c r="G47" s="73">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>6.4</v>
       </c>
       <c r="H47" s="6" t="s">
@@ -34105,14 +34121,14 @@
         <v>95</v>
       </c>
       <c r="J47" s="23">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>608</v>
       </c>
       <c r="K47" s="1">
         <v>22</v>
       </c>
       <c r="L47" s="73">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>3.4375</v>
       </c>
       <c r="M47" s="6">
@@ -34136,7 +34152,7 @@
         <v>57</v>
       </c>
       <c r="G48" s="73">
-        <f t="shared" ref="G48:G50" si="73">E48/C48</f>
+        <f t="shared" ref="G48:G50" si="72">E48/C48</f>
         <v>6.333333333333333</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -34177,7 +34193,7 @@
         <v>48</v>
       </c>
       <c r="G49" s="73">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>4.3636363636363633</v>
       </c>
       <c r="H49" s="6" t="s">
@@ -34187,14 +34203,14 @@
         <v>369</v>
       </c>
       <c r="J49" s="23">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>1610.181818181818</v>
       </c>
       <c r="K49" s="6">
         <v>15</v>
       </c>
       <c r="L49" s="73">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>3.4375000000000004</v>
       </c>
       <c r="M49" s="6">
@@ -34212,7 +34228,7 @@
         <v>72</v>
       </c>
       <c r="G50" s="73">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>5.1428571428571432</v>
       </c>
       <c r="H50" s="6" t="s">
@@ -34229,7 +34245,7 @@
         <v>16.5</v>
       </c>
       <c r="L50" s="73">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>3.208333333333333</v>
       </c>
       <c r="M50" s="6">
@@ -34259,7 +34275,7 @@
         <v>57</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" ref="G52:G54" si="74">E52/C52</f>
+        <f t="shared" ref="G52:G54" si="73">E52/C52</f>
         <v>3</v>
       </c>
       <c r="H52" s="6" t="s">
@@ -34306,7 +34322,7 @@
         <v>57</v>
       </c>
       <c r="G53" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>3</v>
       </c>
       <c r="H53" s="6" t="s">
@@ -34353,7 +34369,7 @@
         <v>57</v>
       </c>
       <c r="G54" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>3</v>
       </c>
       <c r="H54" s="6" t="s">
@@ -34363,14 +34379,14 @@
         <v>95</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" ref="J54" si="75">I54*G54</f>
+        <f t="shared" ref="J54" si="74">I54*G54</f>
         <v>285</v>
       </c>
       <c r="K54" s="1">
         <v>22</v>
       </c>
       <c r="L54" s="73">
-        <f t="shared" ref="L54" si="76">K54/G54</f>
+        <f t="shared" ref="L54" si="75">K54/G54</f>
         <v>7.333333333333333</v>
       </c>
       <c r="M54" s="6">
@@ -34405,7 +34421,7 @@
       </c>
       <c r="F56" s="70"/>
       <c r="G56" s="70">
-        <f t="shared" ref="G56" si="77">E56/C56</f>
+        <f t="shared" ref="G56" si="76">E56/C56</f>
         <v>3</v>
       </c>
       <c r="H56" s="70" t="s">
@@ -34422,7 +34438,7 @@
         <v>28</v>
       </c>
       <c r="L56" s="74">
-        <f t="shared" ref="L56" si="78">K56/G56</f>
+        <f t="shared" ref="L56" si="77">K56/G56</f>
         <v>9.3333333333333339</v>
       </c>
       <c r="M56" s="70">
@@ -34455,7 +34471,7 @@
       </c>
       <c r="F57" s="70"/>
       <c r="G57" s="70">
-        <f t="shared" ref="G57" si="79">E57/C57</f>
+        <f t="shared" ref="G57" si="78">E57/C57</f>
         <v>3.8</v>
       </c>
       <c r="H57" s="70" t="s">
@@ -34472,7 +34488,7 @@
         <v>28</v>
       </c>
       <c r="L57" s="74">
-        <f t="shared" ref="L57" si="80">K57/G57</f>
+        <f t="shared" ref="L57" si="79">K57/G57</f>
         <v>7.3684210526315796</v>
       </c>
       <c r="M57" s="70">
@@ -34525,7 +34541,7 @@
         <v>28</v>
       </c>
       <c r="L59" s="73">
-        <f t="shared" ref="L59" si="81">K59/G59</f>
+        <f t="shared" ref="L59" si="80">K59/G59</f>
         <v>9.3333333333333339</v>
       </c>
       <c r="M59" s="6">
@@ -34545,19 +34561,19 @@
       <c r="X59" s="77"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H64" s="162" t="s">
+      <c r="H64" s="164" t="s">
         <v>525</v>
       </c>
-      <c r="I64" s="162"/>
-      <c r="J64" s="162"/>
-      <c r="K64" s="162"/>
-      <c r="L64" s="162"/>
-      <c r="M64" s="162"/>
-      <c r="N64" s="162"/>
-      <c r="O64" s="162"/>
-      <c r="P64" s="162"/>
-      <c r="Q64" s="162"/>
-      <c r="R64" s="162"/>
+      <c r="I64" s="164"/>
+      <c r="J64" s="164"/>
+      <c r="K64" s="164"/>
+      <c r="L64" s="164"/>
+      <c r="M64" s="164"/>
+      <c r="N64" s="164"/>
+      <c r="O64" s="164"/>
+      <c r="P64" s="164"/>
+      <c r="Q64" s="164"/>
+      <c r="R64" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4626" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59DD4D9C-384B-4AC4-9D74-85AC71B7BA87}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615F0E69-C297-4706-B87C-722E587A44A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70" yWindow="190" windowWidth="27140" windowHeight="17750" tabRatio="905" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10740" yWindow="850" windowWidth="27340" windowHeight="17520" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -829,7 +829,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3001" uniqueCount="747">
   <si>
     <t>Name</t>
   </si>
@@ -3400,6 +3400,12 @@
   </si>
   <si>
     <t>Motor price</t>
+  </si>
+  <si>
+    <t>95mm  WM95 Plastisol 11.99kg.sqm</t>
+  </si>
+  <si>
+    <t>Croci - AS-55</t>
   </si>
 </sst>
 </file>
@@ -3718,7 +3724,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4179,6 +4185,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -4343,13 +4353,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>574641</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>482600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4431,13 +4441,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>141765</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>12701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>490964</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>495301</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5091,13 +5101,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>83039</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>24424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>510612</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>455929</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5135,13 +5145,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>185987</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>585669</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>482600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5179,13 +5189,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>25924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>543578</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>463550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5223,13 +5233,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>32274</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>530878</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>469900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5267,13 +5277,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>38624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>530878</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5311,13 +5321,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>104865</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>476486</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>489229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5355,13 +5365,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>30719</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>542733</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>444705</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5399,13 +5409,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>550114</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>451055</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5443,13 +5453,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>60714</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>546099</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>440464</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5487,13 +5497,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>51802</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>508223</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>470102</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5531,13 +5541,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>133351</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>508001</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>476702</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5571,6 +5581,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6351</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="375851" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D1C9C5A-C938-4302-9C1F-1B6ED1ADA41E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10537638" y="9613527"/>
+          <a:ext cx="375851" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -12765,7 +12814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E91FF3-79AA-48A9-9F88-C48DFFEF60AE}">
-  <dimension ref="A1:U199"/>
+  <dimension ref="A1:U200"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" bestFit="1" customWidth="1"/>
@@ -13932,10 +13981,10 @@
     </row>
     <row r="22" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
-        <v>41</v>
+        <v>745</v>
       </c>
       <c r="B22" s="5">
-        <v>12</v>
+        <v>11.99</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
@@ -13954,21 +14003,23 @@
         <v>10</v>
       </c>
       <c r="I22" s="5">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="J22" s="41">
         <v>127</v>
       </c>
       <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
+      <c r="L22" s="41">
+        <v>0</v>
+      </c>
       <c r="N22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="6" t="s">
-        <v>39</v>
+      <c r="P22" s="6">
+        <v>3.2</v>
       </c>
       <c r="Q22" s="49" t="s">
         <v>20</v>
@@ -13986,171 +14037,173 @@
         <v>661</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="61" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="89" t="s">
+    <row r="23" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5">
+        <v>12</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5">
+        <v>94</v>
+      </c>
+      <c r="E23" s="5">
+        <v>95</v>
+      </c>
+      <c r="F23" s="5">
+        <v>50</v>
+      </c>
+      <c r="G23" s="5">
+        <v>25</v>
+      </c>
+      <c r="H23" s="27">
+        <v>10</v>
+      </c>
+      <c r="I23" s="5">
+        <v>9000</v>
+      </c>
+      <c r="J23" s="41">
+        <v>127</v>
+      </c>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="N23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q23" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="T23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U23" s="47" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="61" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="62"/>
-    </row>
-    <row r="24" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="66"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="62"/>
+    </row>
+    <row r="25" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B25" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C25" s="5">
         <v>0.91</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D25" s="5">
         <v>98</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E25" s="5">
         <v>102</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
         <v>25</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H25" s="27">
         <v>10</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I25" s="5">
         <v>9000</v>
       </c>
-      <c r="J24" s="41">
+      <c r="J25" s="41">
         <v>100</v>
       </c>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41">
+      <c r="K25" s="41"/>
+      <c r="L25" s="41">
         <v>0</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="N25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="O25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P25" s="6">
         <v>4.3</v>
       </c>
-      <c r="Q24" s="49" t="s">
+      <c r="Q25" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="R24" s="6" t="s">
+      <c r="R25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S24" s="19" t="s">
+      <c r="S25" s="19" t="s">
         <v>545</v>
       </c>
-      <c r="T24" s="6" t="s">
+      <c r="T25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U24" s="47" t="s">
+      <c r="U25" s="47" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="89" t="s">
+    <row r="26" spans="1:21" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="62"/>
-    </row>
-    <row r="26" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="52">
-        <v>40</v>
-      </c>
-      <c r="E26" s="52">
-        <v>42</v>
-      </c>
-      <c r="F26" s="52">
-        <v>130</v>
-      </c>
-      <c r="G26" s="52">
-        <v>9</v>
-      </c>
-      <c r="H26" s="54">
-        <v>10</v>
-      </c>
-      <c r="I26" s="34">
-        <v>3800</v>
-      </c>
-      <c r="J26" s="6">
-        <v>60</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q26" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S26" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="T26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U26" s="47" t="s">
-        <v>156</v>
-      </c>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="62"/>
     </row>
     <row r="27" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="26" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="52">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E27" s="52">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F27" s="52">
         <v>130</v>
@@ -14162,7 +14215,7 @@
         <v>10</v>
       </c>
       <c r="I27" s="34">
-        <v>5000</v>
+        <v>3800</v>
       </c>
       <c r="J27" s="6">
         <v>60</v>
@@ -14183,7 +14236,7 @@
         <v>17</v>
       </c>
       <c r="S27" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="T27" s="6" t="s">
         <v>17</v>
@@ -14194,10 +14247,10 @@
     </row>
     <row r="28" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="5">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="52">
@@ -14216,7 +14269,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="34">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="J28" s="6">
         <v>60</v>
@@ -14248,7 +14301,7 @@
     </row>
     <row r="29" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="5">
         <v>6.5</v>
@@ -14302,10 +14355,10 @@
     </row>
     <row r="30" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="5">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="52">
@@ -14356,29 +14409,29 @@
     </row>
     <row r="31" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="5">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="52">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E31" s="52">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F31" s="52">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="G31" s="52">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H31" s="54">
         <v>10</v>
       </c>
       <c r="I31" s="34">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="J31" s="6">
         <v>60</v>
@@ -14399,7 +14452,7 @@
         <v>17</v>
       </c>
       <c r="S31" s="19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>17</v>
@@ -14410,25 +14463,25 @@
     </row>
     <row r="32" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="34">
-        <v>9.25</v>
-      </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="53">
-        <v>77.3</v>
-      </c>
-      <c r="E32" s="53">
-        <v>79</v>
+        <v>50</v>
+      </c>
+      <c r="B32" s="5">
+        <v>9</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="52">
+        <v>55</v>
+      </c>
+      <c r="E32" s="52">
+        <v>59</v>
       </c>
       <c r="F32" s="52">
         <v>170</v>
       </c>
-      <c r="G32" s="53">
-        <v>19</v>
-      </c>
-      <c r="H32" s="53">
+      <c r="G32" s="52">
+        <v>15</v>
+      </c>
+      <c r="H32" s="54">
         <v>10</v>
       </c>
       <c r="I32" s="34">
@@ -14453,7 +14506,7 @@
         <v>17</v>
       </c>
       <c r="S32" s="19" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="T32" s="6" t="s">
         <v>17</v>
@@ -14464,10 +14517,10 @@
     </row>
     <row r="33" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="34">
-        <v>7</v>
+        <v>9.25</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="53">
@@ -14518,10 +14571,10 @@
     </row>
     <row r="34" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="53">
@@ -14572,29 +14625,29 @@
     </row>
     <row r="35" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="53">
-        <v>88</v>
+        <v>77.3</v>
       </c>
       <c r="E35" s="53">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F35" s="52">
         <v>170</v>
       </c>
       <c r="G35" s="53">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H35" s="53">
         <v>10</v>
       </c>
       <c r="I35" s="34">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="J35" s="6">
         <v>60</v>
@@ -14606,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="Q35" s="49" t="s">
         <v>45</v>
@@ -14615,7 +14668,7 @@
         <v>17</v>
       </c>
       <c r="S35" s="19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T35" s="6" t="s">
         <v>17</v>
@@ -14624,104 +14677,105 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="61" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="89" t="s">
+    <row r="36" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="34">
+        <v>7</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="53">
+        <v>88</v>
+      </c>
+      <c r="E36" s="53">
+        <v>90</v>
+      </c>
+      <c r="F36" s="52">
+        <v>170</v>
+      </c>
+      <c r="G36" s="53">
+        <v>27</v>
+      </c>
+      <c r="H36" s="53">
+        <v>10</v>
+      </c>
+      <c r="I36" s="34">
+        <v>5000</v>
+      </c>
+      <c r="J36" s="6">
+        <v>60</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q36" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S36" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="T36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U36" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" s="61" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="59"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="60"/>
-      <c r="N36" s="60"/>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
-      <c r="Q36" s="62"/>
-    </row>
-    <row r="37" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="34">
-        <v>5</v>
-      </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="53">
-        <v>77</v>
-      </c>
-      <c r="E37" s="53">
-        <v>79</v>
-      </c>
-      <c r="F37" s="124">
-        <v>200</v>
-      </c>
-      <c r="G37" s="53">
-        <v>21</v>
-      </c>
-      <c r="H37" s="53">
-        <v>10</v>
-      </c>
-      <c r="I37" s="34">
-        <v>5400</v>
-      </c>
-      <c r="J37" s="6">
-        <v>60</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q37" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="R37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S37" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="T37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U37" s="47" t="s">
-        <v>156</v>
-      </c>
+      <c r="B37" s="59"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="60"/>
+      <c r="Q37" s="62"/>
     </row>
     <row r="38" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="D38" s="88">
-        <v>55</v>
-      </c>
-      <c r="E38" s="88">
-        <v>57</v>
-      </c>
-      <c r="F38" s="125">
-        <v>150</v>
-      </c>
-      <c r="G38" s="88">
-        <v>14</v>
-      </c>
-      <c r="H38" s="88">
+        <v>56</v>
+      </c>
+      <c r="B38" s="34">
+        <v>5</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="53">
+        <v>77</v>
+      </c>
+      <c r="E38" s="53">
+        <v>79</v>
+      </c>
+      <c r="F38" s="124">
+        <v>200</v>
+      </c>
+      <c r="G38" s="53">
+        <v>21</v>
+      </c>
+      <c r="H38" s="53">
         <v>10</v>
       </c>
-      <c r="I38" s="6">
-        <v>3000</v>
+      <c r="I38" s="34">
+        <v>5400</v>
       </c>
       <c r="J38" s="6">
         <v>60</v>
@@ -14742,7 +14796,7 @@
         <v>17</v>
       </c>
       <c r="S38" s="19" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="T38" s="6" t="s">
         <v>17</v>
@@ -14751,8 +14805,112 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="D39" s="88">
+        <v>55</v>
+      </c>
+      <c r="E39" s="88">
+        <v>57</v>
+      </c>
+      <c r="F39" s="125">
+        <v>150</v>
+      </c>
+      <c r="G39" s="88">
+        <v>14</v>
+      </c>
+      <c r="H39" s="88">
+        <v>10</v>
+      </c>
+      <c r="I39" s="6">
+        <v>3000</v>
+      </c>
+      <c r="J39" s="6">
+        <v>60</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q39" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S39" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="T39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U39" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="165" t="s">
+        <v>746</v>
+      </c>
+      <c r="B40" s="6">
+        <v>10</v>
+      </c>
+      <c r="D40" s="88">
+        <v>55</v>
+      </c>
+      <c r="E40" s="88">
+        <v>57</v>
+      </c>
+      <c r="F40" s="125">
+        <v>150</v>
+      </c>
+      <c r="G40" s="88">
+        <v>14</v>
+      </c>
+      <c r="H40" s="88">
+        <v>10</v>
+      </c>
+      <c r="I40" s="6">
+        <v>4200</v>
+      </c>
+      <c r="J40" s="6">
+        <v>60</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q40" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S40" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="T40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U40" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
     <row r="41" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="43" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14912,6 +15070,7 @@
     <row r="197" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="198" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="199" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
